--- a/xls/square_un_16_tri3_17.xlsx
+++ b/xls/square_un_16_tri3_17.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>380</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>340</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>297</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>1596</v>
+      </c>
+      <c r="I15">
+        <v>-0.00019477406914870677</v>
+      </c>
+      <c r="J15">
+        <v>-0.9897648565598229</v>
+      </c>
+      <c r="K15">
+        <v>1.3835347928039812</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>380</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>340</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>340</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>1842</v>
+      </c>
+      <c r="I16">
+        <v>-0.0001623560714966778</v>
+      </c>
+      <c r="J16">
+        <v>-0.6731679724207026</v>
+      </c>
+      <c r="K16">
+        <v>2.247831896032667</v>
+      </c>
+    </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F17">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17">
-        <v>1734</v>
+        <v>2070</v>
       </c>
       <c r="I17">
-        <v>-2.1331023156984683</v>
+        <v>-0.00016035104892954272</v>
       </c>
       <c r="J17">
-        <v>-2.175440639649655</v>
+        <v>-0.6321684028623767</v>
       </c>
       <c r="K17">
-        <v>-0.6228238918980562</v>
+        <v>2.6111506604772696</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>361</v>
+        <v>435</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>1944</v>
+        <v>2388</v>
       </c>
       <c r="I18">
-        <v>-2.378629735412297</v>
+        <v>-4.492733748614717e-5</v>
       </c>
       <c r="J18">
-        <v>-2.2272325976847744</v>
+        <v>-0.1319858026475964</v>
       </c>
       <c r="K18">
-        <v>-0.35235726177853666</v>
+        <v>3.1321706303705437</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>2166</v>
+        <v>2676</v>
       </c>
       <c r="I19">
-        <v>-2.4869596344090166</v>
+        <v>-1.205783917594347e-7</v>
       </c>
       <c r="J19">
-        <v>-2.041497441019321</v>
+        <v>-0.0003146042133569798</v>
       </c>
       <c r="K19">
-        <v>0.5915850721685294</v>
+        <v>2.6492180146166735</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>-1.7377824138493754</v>
+        <v>-4.881258593390645e-9</v>
       </c>
       <c r="J20">
-        <v>-1.4733466645472404</v>
+        <v>-8.208597801144698e-6</v>
       </c>
       <c r="K20">
-        <v>1.5998574142728847</v>
+        <v>1.8701060847253743</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-0.3288507401789058</v>
+        <v>-3.2092978283831284e-9</v>
       </c>
       <c r="J21">
-        <v>-0.2953099627706431</v>
+        <v>-5.41786243998945e-6</v>
       </c>
       <c r="K21">
-        <v>2.517870904406713</v>
+        <v>1.791423498323751</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-0.004473578385159406</v>
+        <v>-2.031976839936566e-9</v>
       </c>
       <c r="J22">
-        <v>-0.007552619852555731</v>
+        <v>-3.458727554005525e-6</v>
       </c>
       <c r="K22">
-        <v>3.252887325175802</v>
+        <v>1.6933899923462685</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-0.00029386050111249076</v>
+        <v>-8.210125426126859e-10</v>
       </c>
       <c r="J23">
-        <v>-0.00036297834917634194</v>
+        <v>-1.448409302492381e-6</v>
       </c>
       <c r="K23">
-        <v>2.7744607167806072</v>
+        <v>1.5169541472755392</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-7.58111258940498e-5</v>
+        <v>-8.924293813007979e-10</v>
       </c>
       <c r="J24">
-        <v>-0.00010198217592302867</v>
+        <v>-1.5961933616070169e-6</v>
       </c>
       <c r="K24">
-        <v>2.5175725364471235</v>
+        <v>1.535407284059581</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-5.816909449165543e-5</v>
+        <v>-6.403565437012326e-10</v>
       </c>
       <c r="J25">
-        <v>-7.284213126035124e-5</v>
+        <v>-1.223997946793228e-6</v>
       </c>
       <c r="K25">
-        <v>2.4289222662529326</v>
+        <v>1.4887765034686797</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-3.525860955397692e-5</v>
+        <v>-5.663748350720547e-10</v>
       </c>
       <c r="J26">
-        <v>-4.44015426333776e-5</v>
+        <v>-1.0031963469902834e-6</v>
       </c>
       <c r="K26">
-        <v>2.324646490304115</v>
+        <v>1.4384627989493446</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-2.827330294085668e-5</v>
+        <v>-4.661270159743821e-10</v>
       </c>
       <c r="J27">
-        <v>-3.514945571970684e-5</v>
+        <v>-8.525384112063074e-7</v>
       </c>
       <c r="K27">
-        <v>2.2719870383272753</v>
+        <v>1.4058017327667751</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-2.0399871541549778e-5</v>
+        <v>-4.081387748551528e-10</v>
       </c>
       <c r="J28">
-        <v>-2.591846657450695e-5</v>
+        <v>-7.622055240692349e-7</v>
       </c>
       <c r="K28">
-        <v>2.2096078825766496</v>
+        <v>1.3849536420008361</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-1.568166688690837e-5</v>
+        <v>-4.1216913328904526e-10</v>
       </c>
       <c r="J29">
-        <v>-1.9939671064758788e-5</v>
+        <v>-7.843644813572845e-7</v>
       </c>
       <c r="K29">
-        <v>2.153755749229193</v>
+        <v>1.3915981270973454</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -928,22 +998,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-1.2756926154525456e-5</v>
+        <v>-3.5058129882332306e-10</v>
       </c>
       <c r="J30">
-        <v>-1.6239008142942837e-5</v>
+        <v>-6.659140914774812e-7</v>
       </c>
       <c r="K30">
-        <v>2.1102039636992322</v>
+        <v>1.3569278140497956</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -963,22 +1033,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-1.0629273025954292e-5</v>
+        <v>-3.346032123682774e-10</v>
       </c>
       <c r="J31">
-        <v>-1.369311540711651e-5</v>
+        <v>-6.339609782706792e-7</v>
       </c>
       <c r="K31">
-        <v>2.0746151088631186</v>
+        <v>1.3453891378592393</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -998,22 +1068,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-1.1353862704094034e-5</v>
+        <v>-3.0450351448348235e-10</v>
       </c>
       <c r="J32">
-        <v>-1.4745594386603532e-5</v>
+        <v>-5.817186216441658e-7</v>
       </c>
       <c r="K32">
-        <v>2.091896949799101</v>
+        <v>1.3287406928871937</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_17.xlsx
+++ b/xls/square_un_16_tri3_17.xlsx
@@ -482,13 +482,13 @@
         <v>1596</v>
       </c>
       <c r="I15">
-        <v>-0.00019477406914870677</v>
+        <v>-1.8190826758416998</v>
       </c>
       <c r="J15">
-        <v>-0.9897648565598229</v>
+        <v>-1.9810379991445983</v>
       </c>
       <c r="K15">
-        <v>1.3835347928039812</v>
+        <v>-0.9091469526711623</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-0.0001623560714966778</v>
+        <v>-2.308536985802335</v>
       </c>
       <c r="J16">
-        <v>-0.6731679724207026</v>
+        <v>-1.9783702609297933</v>
       </c>
       <c r="K16">
-        <v>2.247831896032667</v>
+        <v>-0.8163750951803799</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2070</v>
       </c>
       <c r="I17">
-        <v>-0.00016035104892954272</v>
+        <v>-1.9547022178456719</v>
       </c>
       <c r="J17">
-        <v>-0.6321684028623767</v>
+        <v>-1.6367866150850419</v>
       </c>
       <c r="K17">
-        <v>2.6111506604772696</v>
+        <v>0.2307908929226108</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2388</v>
       </c>
       <c r="I18">
-        <v>-4.492733748614717e-5</v>
+        <v>-1.0922235889941434</v>
       </c>
       <c r="J18">
-        <v>-0.1319858026475964</v>
+        <v>-0.938481463831685</v>
       </c>
       <c r="K18">
-        <v>3.1321706303705437</v>
+        <v>1.2061744504597096</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-1.205783917594347e-7</v>
+        <v>-0.2619687814705875</v>
       </c>
       <c r="J19">
-        <v>-0.0003146042133569798</v>
+        <v>-0.22950468816907946</v>
       </c>
       <c r="K19">
-        <v>2.6492180146166735</v>
+        <v>2.188901933443743</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -657,13 +657,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-4.881258593390645e-9</v>
+        <v>-4.472474150918763e-6</v>
       </c>
       <c r="J20">
-        <v>-8.208597801144698e-6</v>
+        <v>-1.1464857816121937e-5</v>
       </c>
       <c r="K20">
-        <v>1.8701060847253743</v>
+        <v>2.0848045968824915</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -692,13 +692,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-3.2092978283831284e-9</v>
+        <v>-2.876204954354398e-7</v>
       </c>
       <c r="J21">
-        <v>-5.41786243998945e-6</v>
+        <v>-4.568013040913406e-6</v>
       </c>
       <c r="K21">
-        <v>1.791423498323751</v>
+        <v>1.9430875414291509</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -727,13 +727,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-2.031976839936566e-9</v>
+        <v>-4.70248864817141e-6</v>
       </c>
       <c r="J22">
-        <v>-3.458727554005525e-6</v>
+        <v>-4.6640507555674775e-6</v>
       </c>
       <c r="K22">
-        <v>1.6933899923462685</v>
+        <v>1.7799265583798982</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -762,13 +762,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-8.210125426126859e-10</v>
+        <v>-1.3744642904763556e-6</v>
       </c>
       <c r="J23">
-        <v>-1.448409302492381e-6</v>
+        <v>-1.5641020244561746e-6</v>
       </c>
       <c r="K23">
-        <v>1.5169541472755392</v>
+        <v>1.5734781195671415</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -797,13 +797,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-8.924293813007979e-10</v>
+        <v>-2.1832468247102267e-6</v>
       </c>
       <c r="J24">
-        <v>-1.5961933616070169e-6</v>
+        <v>-2.0396058928675465e-6</v>
       </c>
       <c r="K24">
-        <v>1.535407284059581</v>
+        <v>1.5830246859187254</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -832,13 +832,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-6.403565437012326e-10</v>
+        <v>-1.7572134402052066e-6</v>
       </c>
       <c r="J25">
-        <v>-1.223997946793228e-6</v>
+        <v>-1.6029121579362847e-6</v>
       </c>
       <c r="K25">
-        <v>1.4887765034686797</v>
+        <v>1.5221579113569816</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -867,13 +867,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-5.663748350720547e-10</v>
+        <v>-1.080901145119357e-6</v>
       </c>
       <c r="J26">
-        <v>-1.0031963469902834e-6</v>
+        <v>-1.0939665262301951e-6</v>
       </c>
       <c r="K26">
-        <v>1.4384627989493446</v>
+        <v>1.470051203063649</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -902,13 +902,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-4.661270159743821e-10</v>
+        <v>-9.697335813701949e-7</v>
       </c>
       <c r="J27">
-        <v>-8.525384112063074e-7</v>
+        <v>-9.63106678186427e-7</v>
       </c>
       <c r="K27">
-        <v>1.4058017327667751</v>
+        <v>1.437430287382646</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -937,13 +937,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-4.081387748551528e-10</v>
+        <v>-8.679434255527084e-7</v>
       </c>
       <c r="J28">
-        <v>-7.622055240692349e-7</v>
+        <v>-8.531558173414517e-7</v>
       </c>
       <c r="K28">
-        <v>1.3849536420008361</v>
+        <v>1.408735818755532</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -972,13 +972,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-4.1216913328904526e-10</v>
+        <v>-1.1098993614825403e-6</v>
       </c>
       <c r="J29">
-        <v>-7.843644813572845e-7</v>
+        <v>-1.0192210656494506e-6</v>
       </c>
       <c r="K29">
-        <v>1.3915981270973454</v>
+        <v>1.4266663340755146</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-3.5058129882332306e-10</v>
+        <v>-8.585797534403343e-7</v>
       </c>
       <c r="J30">
-        <v>-6.659140914774812e-7</v>
+        <v>-8.111035165935925e-7</v>
       </c>
       <c r="K30">
-        <v>1.3569278140497956</v>
+        <v>1.3870760517840135</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-3.346032123682774e-10</v>
+        <v>-9.064563104376035e-7</v>
       </c>
       <c r="J31">
-        <v>-6.339609782706792e-7</v>
+        <v>-8.269860852541423e-7</v>
       </c>
       <c r="K31">
-        <v>1.3453891378592393</v>
+        <v>1.3810688508449636</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-3.0450351448348235e-10</v>
+        <v>-7.675503304235131e-7</v>
       </c>
       <c r="J32">
-        <v>-5.817186216441658e-7</v>
+        <v>-7.11176492468638e-7</v>
       </c>
       <c r="K32">
-        <v>1.3287406928871937</v>
+        <v>1.3525859641136482</v>
       </c>
     </row>
   </sheetData>
